--- a/reporte_asistencias.xlsx
+++ b/reporte_asistencias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,168 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Evidencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13:43:39</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Monitoreo y Control</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Vicos Pajuelo Jilber Ronaldy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20260610_134339_Screenshot_2026-06-09_18421711.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13:39:02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Monitoreo y Control</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Adriana Lianka Tovar Gaspar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20260610_133902_Screenshot_2026-06-09_18421711.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13:37:25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Monitoreo y Control</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Diego Alejandro Castillo Rayme</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20260610_133725_Screenshot_2026-06-09_194708.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13:37:06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Logistica</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Diana Isabel López Camarena</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20260610_133706_Screenshot_2026-06-09_18421711.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:31:07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Monitoreo y Control</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gian Franco Altamirano Torres</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20260610_133107_Screenshot_2026-06-09_18421711.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06:31:25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Monitoreo y Control</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mariana Denisse Mendoza Amaya</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20260610_063125_Screenshot_2026-06-09_18421711.png</t>
         </is>
       </c>
     </row>
